--- a/downloads/dataset.xlsx
+++ b/downloads/dataset.xlsx
@@ -205,7 +205,7 @@
         <v>6.5</v>
       </c>
       <c r="X2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3">
@@ -251,7 +251,7 @@
         <v>3.1</v>
       </c>
       <c r="X3">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="4">
@@ -815,7 +815,7 @@
         <v>4.0</v>
       </c>
       <c r="X12">
-        <v>4.45</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="13">

--- a/downloads/dataset.xlsx
+++ b/downloads/dataset.xlsx
@@ -227,19 +227,19 @@
         <v>6.0</v>
       </c>
       <c r="P3">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="Q3">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="R3">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="S3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T3">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
         <v>3.2</v>

--- a/downloads/dataset.xlsx
+++ b/downloads/dataset.xlsx
@@ -205,7 +205,7 @@
         <v>6.5</v>
       </c>
       <c r="X2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3">
@@ -227,19 +227,19 @@
         <v>6.0</v>
       </c>
       <c r="P3">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="Q3">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="R3">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="S3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T3">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
         <v>3.2</v>
@@ -251,7 +251,7 @@
         <v>3.1</v>
       </c>
       <c r="X3">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="4">
@@ -815,7 +815,7 @@
         <v>4.0</v>
       </c>
       <c r="X12">
-        <v>4.45</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="13">

--- a/downloads/dataset.xlsx
+++ b/downloads/dataset.xlsx
@@ -260,44 +260,32 @@
           <t>youthUnemployment</t>
         </is>
       </c>
-      <c r="L4">
-        <v>13.5</v>
-      </c>
-      <c r="M4">
-        <v>13.8</v>
-      </c>
-      <c r="N4">
-        <v>14.2</v>
-      </c>
       <c r="O4">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="P4">
-        <v>16.1</v>
+        <v>17.3</v>
       </c>
       <c r="Q4">
-        <v>14.8</v>
+        <v>15.0</v>
       </c>
       <c r="R4">
-        <v>17.8</v>
+        <v>12.9</v>
       </c>
       <c r="S4">
-        <v>13.2</v>
+        <v>12.4</v>
       </c>
       <c r="T4">
-        <v>12.9</v>
+        <v>10.0</v>
       </c>
       <c r="U4">
-        <v>12.9</v>
+        <v>10.2</v>
       </c>
       <c r="V4">
-        <v>12.8</v>
+        <v>10.3</v>
       </c>
       <c r="W4">
-        <v>12.5</v>
-      </c>
-      <c r="X4">
-        <v>12.3</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="5">
@@ -306,44 +294,26 @@
           <t>graduateUnemployment</t>
         </is>
       </c>
-      <c r="L5">
-        <v>18.5</v>
-      </c>
-      <c r="M5">
-        <v>19.2</v>
-      </c>
-      <c r="N5">
-        <v>21.0</v>
-      </c>
       <c r="O5">
-        <v>23.5</v>
+        <v>17.2</v>
       </c>
       <c r="P5">
-        <v>25.0</v>
+        <v>16.9</v>
       </c>
       <c r="Q5">
-        <v>23.0</v>
+        <v>17.2</v>
       </c>
       <c r="R5">
-        <v>31.0</v>
+        <v>15.5</v>
       </c>
       <c r="S5">
-        <v>25.0</v>
+        <v>14.9</v>
       </c>
       <c r="T5">
-        <v>22.0</v>
+        <v>13.4</v>
       </c>
       <c r="U5">
-        <v>29.1</v>
-      </c>
-      <c r="V5">
-        <v>28.5</v>
-      </c>
-      <c r="W5">
-        <v>27.0</v>
-      </c>
-      <c r="X5">
-        <v>26.5</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="6">

--- a/downloads/dataset.xlsx
+++ b/downloads/dataset.xlsx
@@ -1068,44 +1068,17 @@
           <t>gigWorkers</t>
         </is>
       </c>
-      <c r="L17">
-        <v>0.8</v>
-      </c>
-      <c r="M17">
-        <v>1.2</v>
-      </c>
-      <c r="N17">
-        <v>1.8</v>
-      </c>
       <c r="O17">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="P17">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q17">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="R17">
-        <v>5.2</v>
-      </c>
-      <c r="S17">
-        <v>6.0</v>
-      </c>
-      <c r="T17">
-        <v>6.8</v>
-      </c>
-      <c r="U17">
-        <v>7.3</v>
-      </c>
-      <c r="V17">
         <v>7.7</v>
-      </c>
-      <c r="W17">
-        <v>8.2</v>
-      </c>
-      <c r="X17">
-        <v>8.8</v>
       </c>
     </row>
     <row r="18">
@@ -1114,44 +1087,11 @@
           <t>ruralIncome</t>
         </is>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>100</v>
       </c>
-      <c r="M18">
-        <v>99</v>
-      </c>
-      <c r="N18">
-        <v>98</v>
-      </c>
-      <c r="O18">
-        <v>97</v>
-      </c>
-      <c r="P18">
-        <v>96</v>
-      </c>
-      <c r="Q18">
-        <v>95</v>
-      </c>
-      <c r="R18">
-        <v>93</v>
-      </c>
       <c r="S18">
-        <v>94</v>
-      </c>
-      <c r="T18">
-        <v>95</v>
-      </c>
-      <c r="U18">
-        <v>96</v>
-      </c>
-      <c r="V18">
-        <v>98</v>
-      </c>
-      <c r="W18">
-        <v>97</v>
-      </c>
-      <c r="X18">
-        <v>97</v>
+        <v>126.8</v>
       </c>
     </row>
     <row r="19">
@@ -1160,44 +1100,32 @@
           <t>femaleLFPR</t>
         </is>
       </c>
-      <c r="L19">
-        <v>22.5</v>
-      </c>
-      <c r="M19">
-        <v>22.0</v>
-      </c>
-      <c r="N19">
-        <v>21.8</v>
-      </c>
       <c r="O19">
-        <v>21.5</v>
+        <v>23.3</v>
       </c>
       <c r="P19">
-        <v>21.2</v>
+        <v>24.5</v>
       </c>
       <c r="Q19">
-        <v>21.0</v>
+        <v>30.0</v>
       </c>
       <c r="R19">
-        <v>20.8</v>
+        <v>32.5</v>
       </c>
       <c r="S19">
-        <v>20.5</v>
+        <v>32.8</v>
       </c>
       <c r="T19">
-        <v>20.3</v>
+        <v>37.0</v>
       </c>
       <c r="U19">
-        <v>20.5</v>
+        <v>41.7</v>
       </c>
       <c r="V19">
-        <v>20.8</v>
+        <v>40.3</v>
       </c>
       <c r="W19">
-        <v>20.9</v>
-      </c>
-      <c r="X19">
-        <v>21.0</v>
+        <v>40.0</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/dataset.xlsx
+++ b/downloads/dataset.xlsx
@@ -260,44 +260,32 @@
           <t>youthUnemployment</t>
         </is>
       </c>
-      <c r="L4">
-        <v>13.5</v>
-      </c>
-      <c r="M4">
-        <v>13.8</v>
-      </c>
-      <c r="N4">
-        <v>14.2</v>
-      </c>
       <c r="O4">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="P4">
-        <v>16.1</v>
+        <v>17.3</v>
       </c>
       <c r="Q4">
-        <v>14.8</v>
+        <v>15.0</v>
       </c>
       <c r="R4">
-        <v>17.8</v>
+        <v>12.9</v>
       </c>
       <c r="S4">
-        <v>13.2</v>
+        <v>12.4</v>
       </c>
       <c r="T4">
-        <v>12.9</v>
+        <v>10.0</v>
       </c>
       <c r="U4">
-        <v>12.9</v>
+        <v>10.2</v>
       </c>
       <c r="V4">
-        <v>12.8</v>
+        <v>10.3</v>
       </c>
       <c r="W4">
-        <v>12.5</v>
-      </c>
-      <c r="X4">
-        <v>12.3</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="5">
@@ -306,44 +294,26 @@
           <t>graduateUnemployment</t>
         </is>
       </c>
-      <c r="L5">
-        <v>18.5</v>
-      </c>
-      <c r="M5">
-        <v>19.2</v>
-      </c>
-      <c r="N5">
-        <v>21.0</v>
-      </c>
       <c r="O5">
-        <v>23.5</v>
+        <v>17.2</v>
       </c>
       <c r="P5">
-        <v>25.0</v>
+        <v>16.9</v>
       </c>
       <c r="Q5">
-        <v>23.0</v>
+        <v>17.2</v>
       </c>
       <c r="R5">
-        <v>31.0</v>
+        <v>15.5</v>
       </c>
       <c r="S5">
-        <v>25.0</v>
+        <v>14.9</v>
       </c>
       <c r="T5">
-        <v>22.0</v>
+        <v>13.4</v>
       </c>
       <c r="U5">
-        <v>29.1</v>
-      </c>
-      <c r="V5">
-        <v>28.5</v>
-      </c>
-      <c r="W5">
-        <v>27.0</v>
-      </c>
-      <c r="X5">
-        <v>26.5</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="6">
@@ -1098,44 +1068,17 @@
           <t>gigWorkers</t>
         </is>
       </c>
-      <c r="L17">
-        <v>0.8</v>
-      </c>
-      <c r="M17">
-        <v>1.2</v>
-      </c>
-      <c r="N17">
-        <v>1.8</v>
-      </c>
       <c r="O17">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="P17">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q17">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="R17">
-        <v>5.2</v>
-      </c>
-      <c r="S17">
-        <v>6.0</v>
-      </c>
-      <c r="T17">
-        <v>6.8</v>
-      </c>
-      <c r="U17">
-        <v>7.3</v>
-      </c>
-      <c r="V17">
         <v>7.7</v>
-      </c>
-      <c r="W17">
-        <v>8.2</v>
-      </c>
-      <c r="X17">
-        <v>8.8</v>
       </c>
     </row>
     <row r="18">
@@ -1144,44 +1087,11 @@
           <t>ruralIncome</t>
         </is>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>100</v>
       </c>
-      <c r="M18">
-        <v>99</v>
-      </c>
-      <c r="N18">
-        <v>98</v>
-      </c>
-      <c r="O18">
-        <v>97</v>
-      </c>
-      <c r="P18">
-        <v>96</v>
-      </c>
-      <c r="Q18">
-        <v>95</v>
-      </c>
-      <c r="R18">
-        <v>93</v>
-      </c>
       <c r="S18">
-        <v>94</v>
-      </c>
-      <c r="T18">
-        <v>95</v>
-      </c>
-      <c r="U18">
-        <v>96</v>
-      </c>
-      <c r="V18">
-        <v>98</v>
-      </c>
-      <c r="W18">
-        <v>97</v>
-      </c>
-      <c r="X18">
-        <v>97</v>
+        <v>126.8</v>
       </c>
     </row>
     <row r="19">
@@ -1190,44 +1100,32 @@
           <t>femaleLFPR</t>
         </is>
       </c>
-      <c r="L19">
-        <v>22.5</v>
-      </c>
-      <c r="M19">
-        <v>22.0</v>
-      </c>
-      <c r="N19">
-        <v>21.8</v>
-      </c>
       <c r="O19">
-        <v>21.5</v>
+        <v>23.3</v>
       </c>
       <c r="P19">
-        <v>21.2</v>
+        <v>24.5</v>
       </c>
       <c r="Q19">
-        <v>21.0</v>
+        <v>30.0</v>
       </c>
       <c r="R19">
-        <v>20.8</v>
+        <v>32.5</v>
       </c>
       <c r="S19">
-        <v>20.5</v>
+        <v>32.8</v>
       </c>
       <c r="T19">
-        <v>20.3</v>
+        <v>37.0</v>
       </c>
       <c r="U19">
-        <v>20.5</v>
+        <v>41.7</v>
       </c>
       <c r="V19">
-        <v>20.8</v>
+        <v>40.3</v>
       </c>
       <c r="W19">
-        <v>20.9</v>
-      </c>
-      <c r="X19">
-        <v>21.0</v>
+        <v>40.0</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/dataset.xlsx
+++ b/downloads/dataset.xlsx
@@ -323,34 +323,34 @@
         </is>
       </c>
       <c r="B6">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="C6">
-        <v>18.8</v>
+        <v>19.3</v>
       </c>
       <c r="D6">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="E6">
         <v>20.1</v>
       </c>
       <c r="F6">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="G6">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="H6">
-        <v>21.0</v>
+        <v>21.2</v>
       </c>
       <c r="I6">
+        <v>21.1</v>
+      </c>
+      <c r="J6">
         <v>21.3</v>
       </c>
-      <c r="J6">
-        <v>21.0</v>
-      </c>
       <c r="K6">
-        <v>21.2</v>
+        <v>21.6</v>
       </c>
       <c r="L6">
         <v>21.3</v>
@@ -359,38 +359,26 @@
         <v>21.7</v>
       </c>
       <c r="N6">
+        <v>22.2</v>
+      </c>
+      <c r="O6">
+        <v>22.3</v>
+      </c>
+      <c r="P6">
+        <v>22.4</v>
+      </c>
+      <c r="Q6">
+        <v>21.6</v>
+      </c>
+      <c r="R6">
         <v>21.5</v>
       </c>
-      <c r="O6">
-        <v>21.5</v>
-      </c>
-      <c r="P6">
+      <c r="S6">
         <v>21.7</v>
-      </c>
-      <c r="Q6">
-        <v>22.1</v>
-      </c>
-      <c r="R6">
-        <v>22.3</v>
-      </c>
-      <c r="S6">
-        <v>22.5</v>
       </c>
       <c r="T6">
         <v>22.6</v>
       </c>
-      <c r="U6">
-        <v>22.6</v>
-      </c>
-      <c r="V6">
-        <v>22.6</v>
-      </c>
-      <c r="W6">
-        <v>22.8</v>
-      </c>
-      <c r="X6">
-        <v>23.0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -399,73 +387,61 @@
         </is>
       </c>
       <c r="B7">
+        <v>18.8</v>
+      </c>
+      <c r="C7">
+        <v>18.4</v>
+      </c>
+      <c r="D7">
+        <v>17.9</v>
+      </c>
+      <c r="E7">
+        <v>17.5</v>
+      </c>
+      <c r="F7">
+        <v>17.0</v>
+      </c>
+      <c r="G7">
         <v>16.5</v>
       </c>
-      <c r="C7">
-        <v>16.3</v>
-      </c>
-      <c r="D7">
+      <c r="H7">
         <v>16.0</v>
-      </c>
-      <c r="E7">
-        <v>15.8</v>
-      </c>
-      <c r="F7">
-        <v>15.6</v>
-      </c>
-      <c r="G7">
-        <v>15.5</v>
-      </c>
-      <c r="H7">
-        <v>15.4</v>
       </c>
       <c r="I7">
         <v>15.3</v>
       </c>
       <c r="J7">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="K7">
-        <v>15.1</v>
+        <v>15.0</v>
       </c>
       <c r="L7">
+        <v>14.7</v>
+      </c>
+      <c r="M7">
+        <v>14.5</v>
+      </c>
+      <c r="N7">
+        <v>14.1</v>
+      </c>
+      <c r="O7">
+        <v>13.9</v>
+      </c>
+      <c r="P7">
+        <v>14.4</v>
+      </c>
+      <c r="Q7">
+        <v>14.7</v>
+      </c>
+      <c r="R7">
+        <v>15.5</v>
+      </c>
+      <c r="S7">
+        <v>15.4</v>
+      </c>
+      <c r="T7">
         <v>15.0</v>
-      </c>
-      <c r="M7">
-        <v>14.7</v>
-      </c>
-      <c r="N7">
-        <v>14.9</v>
-      </c>
-      <c r="O7">
-        <v>14.9</v>
-      </c>
-      <c r="P7">
-        <v>14.7</v>
-      </c>
-      <c r="Q7">
-        <v>13.5</v>
-      </c>
-      <c r="R7">
-        <v>13.3</v>
-      </c>
-      <c r="S7">
-        <v>13.1</v>
-      </c>
-      <c r="T7">
-        <v>13.1</v>
-      </c>
-      <c r="U7">
-        <v>13.1</v>
-      </c>
-      <c r="V7">
-        <v>13.1</v>
-      </c>
-      <c r="W7">
-        <v>13.0</v>
-      </c>
-      <c r="X7">
-        <v>12.9</v>
       </c>
     </row>
     <row r="8">
@@ -474,44 +450,26 @@
           <t>formalEmployment</t>
         </is>
       </c>
-      <c r="L8">
-        <v>13.0</v>
-      </c>
-      <c r="M8">
-        <v>12.8</v>
-      </c>
-      <c r="N8">
-        <v>12.5</v>
-      </c>
       <c r="O8">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="P8">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="Q8">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="R8">
-        <v>11.4</v>
+        <v>9.7</v>
       </c>
       <c r="S8">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="T8">
-        <v>11.3</v>
+        <v>9.6</v>
       </c>
       <c r="U8">
-        <v>11.2</v>
-      </c>
-      <c r="V8">
-        <v>11.2</v>
-      </c>
-      <c r="W8">
-        <v>11.0</v>
-      </c>
-      <c r="X8">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="9">
@@ -520,44 +478,26 @@
           <t>informalEmployment</t>
         </is>
       </c>
-      <c r="L9">
-        <v>87.0</v>
-      </c>
-      <c r="M9">
-        <v>87.2</v>
-      </c>
-      <c r="N9">
-        <v>87.5</v>
-      </c>
       <c r="O9">
-        <v>87.8</v>
+        <v>88.5</v>
       </c>
       <c r="P9">
-        <v>88.1</v>
+        <v>88.6</v>
       </c>
       <c r="Q9">
-        <v>88.4</v>
+        <v>89.5</v>
       </c>
       <c r="R9">
-        <v>88.6</v>
+        <v>90.3</v>
       </c>
       <c r="S9">
-        <v>88.5</v>
+        <v>89.9</v>
       </c>
       <c r="T9">
-        <v>88.7</v>
+        <v>90.4</v>
       </c>
       <c r="U9">
-        <v>88.8</v>
-      </c>
-      <c r="V9">
-        <v>88.8</v>
-      </c>
-      <c r="W9">
-        <v>89.0</v>
-      </c>
-      <c r="X9">
-        <v>89.1</v>
+        <v>89.9</v>
       </c>
     </row>
     <row r="10">
@@ -709,7 +649,7 @@
         <v>4.4</v>
       </c>
       <c r="X11">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="12">
@@ -831,7 +771,7 @@
         <v>87</v>
       </c>
       <c r="X13">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">

--- a/downloads/dataset.xlsx
+++ b/downloads/dataset.xlsx
@@ -531,7 +531,7 @@
         <v>131</v>
       </c>
       <c r="J10">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="K10">
         <v>140</v>
@@ -762,7 +762,7 @@
         <v>79</v>
       </c>
       <c r="U13">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V13">
         <v>84</v>
@@ -847,7 +847,7 @@
         <v>6.55</v>
       </c>
       <c r="X14">
-        <v>6.4</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="15">
@@ -857,73 +857,73 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.0</v>
+        <v>0.28</v>
       </c>
       <c r="C15">
-        <v>0.03</v>
+        <v>0.29</v>
       </c>
       <c r="D15">
-        <v>0.05</v>
+        <v>0.32</v>
       </c>
       <c r="E15">
-        <v>0.07</v>
+        <v>0.35</v>
       </c>
       <c r="F15">
-        <v>0.09</v>
+        <v>0.39</v>
       </c>
       <c r="G15">
-        <v>0.11</v>
+        <v>0.43</v>
       </c>
       <c r="H15">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="I15">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="J15">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="K15">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="L15">
+        <v>0.42</v>
+      </c>
+      <c r="M15">
         <v>0.19</v>
       </c>
-      <c r="M15">
-        <v>0.21</v>
-      </c>
       <c r="N15">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="O15">
+        <v>0.36</v>
+      </c>
+      <c r="P15">
+        <v>0.38</v>
+      </c>
+      <c r="Q15">
+        <v>0.48</v>
+      </c>
+      <c r="R15">
+        <v>0.87</v>
+      </c>
+      <c r="S15">
+        <v>0.58</v>
+      </c>
+      <c r="T15">
+        <v>0.51</v>
+      </c>
+      <c r="U15">
+        <v>0.45</v>
+      </c>
+      <c r="V15">
+        <v>0.44</v>
+      </c>
+      <c r="W15">
         <v>0.41</v>
       </c>
-      <c r="P15">
-        <v>0.53</v>
-      </c>
-      <c r="Q15">
-        <v>0.65</v>
-      </c>
-      <c r="R15">
-        <v>0.92</v>
-      </c>
-      <c r="S15">
-        <v>0.82</v>
-      </c>
-      <c r="T15">
-        <v>0.7</v>
-      </c>
-      <c r="U15">
-        <v>0.68</v>
-      </c>
-      <c r="V15">
-        <v>0.68</v>
-      </c>
-      <c r="W15">
-        <v>0.68</v>
-      </c>
       <c r="X15">
-        <v>0.68</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="16">
@@ -948,7 +948,7 @@
         <v>0.58</v>
       </c>
       <c r="G16">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H16">
         <v>0.56</v>
@@ -957,7 +957,7 @@
         <v>0.54</v>
       </c>
       <c r="J16">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="K16">
         <v>0.51</v>
@@ -999,7 +999,7 @@
         <v>0.3</v>
       </c>
       <c r="X16">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="17">

--- a/downloads/dataset.xlsx
+++ b/downloads/dataset.xlsx
@@ -142,10 +142,10 @@
         <v>7.9</v>
       </c>
       <c r="C2">
-        <v>9.3</v>
+        <v>7.9</v>
       </c>
       <c r="D2">
-        <v>9.3</v>
+        <v>8.1</v>
       </c>
       <c r="E2">
         <v>7.7</v>
@@ -175,36 +175,33 @@
         <v>8.0</v>
       </c>
       <c r="N2">
-        <v>8.2</v>
+        <v>8.3</v>
       </c>
       <c r="O2">
+        <v>6.8</v>
+      </c>
+      <c r="P2">
+        <v>6.5</v>
+      </c>
+      <c r="Q2">
+        <v>3.9</v>
+      </c>
+      <c r="R2">
+        <v>-5.8</v>
+      </c>
+      <c r="S2">
+        <v>9.7</v>
+      </c>
+      <c r="T2">
+        <v>7.6</v>
+      </c>
+      <c r="U2">
+        <v>7.3</v>
+      </c>
+      <c r="V2">
         <v>7.2</v>
       </c>
-      <c r="P2">
-        <v>6.1</v>
-      </c>
-      <c r="Q2">
-        <v>4.2</v>
-      </c>
-      <c r="R2">
-        <v>-7.3</v>
-      </c>
-      <c r="S2">
-        <v>8.7</v>
-      </c>
-      <c r="T2">
-        <v>7.2</v>
-      </c>
-      <c r="U2">
-        <v>7.6</v>
-      </c>
-      <c r="V2">
-        <v>7.8</v>
-      </c>
       <c r="W2">
-        <v>6.5</v>
-      </c>
-      <c r="X2">
         <v>7.8</v>
       </c>
     </row>
@@ -214,15 +211,9 @@
           <t>unemployment</t>
         </is>
       </c>
-      <c r="L3">
-        <v>4.9</v>
-      </c>
       <c r="M3">
         <v>5.0</v>
       </c>
-      <c r="N3">
-        <v>5.0</v>
-      </c>
       <c r="O3">
         <v>6.0</v>
       </c>
@@ -683,10 +674,10 @@
         <v>8.9</v>
       </c>
       <c r="J12">
-        <v>9.3</v>
+        <v>9.5</v>
       </c>
       <c r="K12">
-        <v>10.9</v>
+        <v>10.0</v>
       </c>
       <c r="L12">
         <v>6.7</v>
@@ -695,34 +686,34 @@
         <v>4.9</v>
       </c>
       <c r="N12">
-        <v>4.5</v>
+        <v>5.0</v>
       </c>
       <c r="O12">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q12">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="R12">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="S12">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="T12">
         <v>6.7</v>
       </c>
       <c r="U12">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="V12">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="W12">
-        <v>4.0</v>
+        <v>2.2</v>
       </c>
       <c r="X12">
         <v>3.8</v>
@@ -820,16 +811,16 @@
         <v>1.05</v>
       </c>
       <c r="O14">
-        <v>2.05</v>
+        <v>1.05</v>
       </c>
       <c r="P14">
-        <v>4.0</v>
+        <v>1.8</v>
       </c>
       <c r="Q14">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="R14">
-        <v>7.0</v>
+        <v>7.3</v>
       </c>
       <c r="S14">
         <v>9.0</v>

--- a/downloads/dataset.xlsx
+++ b/downloads/dataset.xlsx
@@ -196,13 +196,13 @@
         <v>7.6</v>
       </c>
       <c r="U2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="V2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="W2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3">
@@ -639,9 +639,6 @@
       <c r="W11">
         <v>4.4</v>
       </c>
-      <c r="X11">
-        <v>4.3</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -713,7 +710,7 @@
         <v>4.9</v>
       </c>
       <c r="W12">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="X12">
         <v>3.8</v>
@@ -1007,9 +1004,6 @@
       </c>
       <c r="Q17">
         <v>6.8</v>
-      </c>
-      <c r="R17">
-        <v>7.7</v>
       </c>
     </row>
     <row r="18">

--- a/downloads/dataset.xlsx
+++ b/downloads/dataset.xlsx
@@ -242,7 +242,7 @@
         <v>3.1</v>
       </c>
       <c r="X3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="4">
@@ -713,7 +713,7 @@
         <v>2.4</v>
       </c>
       <c r="X12">
-        <v>3.8</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="13">
